--- a/data/trans_dic/IP11C$medico-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$medico-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y consultaron a un médico/a o enfermero/a</t>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y consultaron a un médico/a o enfermero/a (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -876,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,23</t>
+          <t>0,0; 50,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,78</t>
+          <t>0,0; 71,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,11</t>
+          <t>0,0; 44,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,01</t>
+          <t>0,0; 67,44</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,55</t>
+          <t>0,0; 65,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,53; 59,13</t>
+          <t>7,72; 58,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,17</t>
+          <t>0,0; 44,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 46,81</t>
+          <t>9,51; 48,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,06</t>
+          <t>0,0; 26,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 36,79</t>
+          <t>4,55; 38,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,17</t>
+          <t>0,0; 40,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 40,73</t>
+          <t>5,11; 37,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 33,12</t>
+          <t>7,46; 35,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 43,71</t>
+          <t>5,21; 44,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 31,95</t>
+          <t>7,25; 32,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 21,49</t>
+          <t>4,42; 20,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 30,62</t>
+          <t>3,18; 29,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,16</t>
+          <t>0,0; 21,74</t>
         </is>
       </c>
     </row>
@@ -1276,37 +1277,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,42</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 42,5</t>
+          <t>4,48; 38,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,41</t>
+          <t>0,0; 35,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,29</t>
+          <t>0,0; 33,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1316,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 35,76</t>
+          <t>4,67; 38,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 27,3</t>
+          <t>5,09; 27,48</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,48</t>
+          <t>0,0; 74,91</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,05</t>
+          <t>0,0; 39,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,33</t>
+          <t>0,0; 35,39</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,81; 22,06</t>
+          <t>3,88; 22,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 12,56</t>
+          <t>1,22; 12,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,83</t>
+          <t>0,0; 30,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 24,52</t>
+          <t>6,62; 23,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,73; 17,88</t>
+          <t>5,77; 16,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 17,83</t>
+          <t>1,75; 16,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,69</t>
+          <t>0,0; 31,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,31; 19,08</t>
+          <t>7,18; 19,28</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,55; 12,5</t>
+          <t>4,48; 12,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,25</t>
+          <t>1,19; 10,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,22; 24,39</t>
+          <t>3,24; 23,58</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y consultaron a un médico/a o enfermero/a (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2510</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2533</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2974</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5181</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3567</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6573</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2516</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3095</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2476</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>665; 5030</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2726</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1178; 6023</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3318</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2036</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4241</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4241</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>579; 4911</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2145</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>742; 5512</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1810; 8573</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>643; 5463</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1977; 8846</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1772; 8343</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>649; 5949</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2711</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2236</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2128</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3589</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2856</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>594; 5086</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4004</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4514</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1826</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>656; 5405</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1365; 7365</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3373</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1091</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1091</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3627</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3989</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2236</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>6195</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>7358</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2439</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>9617</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>9595</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>3841</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>1321; 7516</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>607; 6363</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5252</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2989; 10630</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4123; 12028</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>715; 6852</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 7475</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>5691; 15282</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>5425; 15276</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>746; 6893</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1334; 9712</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$medico-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$medico-Clase-trans_dic.xlsx
@@ -887,12 +887,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,38</t>
+          <t>0,0; 49,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,83</t>
+          <t>0,0; 66,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,77</t>
+          <t>0,0; 46,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,44</t>
+          <t>0,0; 61,76</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,55</t>
+          <t>0,0; 65,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,72; 58,38</t>
+          <t>7,49; 58,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,89</t>
+          <t>0,0; 56,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 48,6</t>
+          <t>9,61; 50,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,96</t>
+          <t>0,0; 27,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 38,62</t>
+          <t>4,65; 38,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1152,22 +1152,22 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,32</t>
+          <t>0,0; 39,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 37,93</t>
+          <t>5,06; 41,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 35,34</t>
+          <t>7,08; 35,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,21; 44,3</t>
+          <t>5,25; 44,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,22 +1177,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 32,46</t>
+          <t>7,59; 32,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,42; 20,8</t>
+          <t>4,47; 22,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 29,2</t>
+          <t>3,15; 26,89</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,74</t>
+          <t>0,0; 18,24</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,48; 38,36</t>
+          <t>4,72; 39,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,78</t>
+          <t>0,0; 38,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,34</t>
+          <t>0,0; 31,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,67; 38,48</t>
+          <t>4,69; 40,02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,09; 27,48</t>
+          <t>4,93; 28,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,91</t>
+          <t>0,0; 67,77</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,3</t>
+          <t>0,0; 38,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,39</t>
+          <t>0,0; 30,45</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,88; 22,05</t>
+          <t>3,81; 21,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 12,78</t>
+          <t>1,22; 11,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,47 +1572,47 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,62</t>
+          <t>0,0; 30,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,62; 23,54</t>
+          <t>6,75; 23,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,77; 16,83</t>
+          <t>5,25; 17,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 16,83</t>
+          <t>1,82; 17,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,1</t>
+          <t>0,0; 29,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,18; 19,28</t>
+          <t>7,0; 18,94</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 12,6</t>
+          <t>4,49; 12,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,97</t>
+          <t>1,6; 12,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 23,58</t>
+          <t>2,53; 24,69</t>
         </is>
       </c>
     </row>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2974</t>
+          <t>0; 2942</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5181</t>
+          <t>0; 4777</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3567</t>
+          <t>0; 3723</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 6573</t>
+          <t>0; 6019</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>665; 5030</t>
+          <t>645; 5024</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2726</t>
+          <t>0; 3411</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1178; 6023</t>
+          <t>1191; 6275</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 3318</t>
+          <t>0; 3383</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>579; 4911</t>
+          <t>592; 4851</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2566,22 +2566,22 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2145</t>
+          <t>0; 2109</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>742; 5512</t>
+          <t>736; 6018</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1810; 8573</t>
+          <t>1717; 8520</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>643; 5463</t>
+          <t>647; 5468</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2591,22 +2591,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1977; 8846</t>
+          <t>2067; 8857</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1772; 8343</t>
+          <t>1791; 9129</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>649; 5949</t>
+          <t>642; 5478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 2711</t>
+          <t>0; 2275</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>594; 5086</t>
+          <t>625; 5173</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4004</t>
+          <t>0; 4346</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4514</t>
+          <t>0; 4260</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>656; 5405</t>
+          <t>659; 5622</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1365; 7365</t>
+          <t>1320; 7614</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3373</t>
+          <t>0; 3052</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3627</t>
+          <t>0; 3542</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 3989</t>
+          <t>0; 3433</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1321; 7516</t>
+          <t>1300; 7195</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>607; 6363</t>
+          <t>609; 5913</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3190,47 +3190,47 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 5252</t>
+          <t>0; 5219</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2989; 10630</t>
+          <t>3047; 10815</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4123; 12028</t>
+          <t>3750; 12343</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>715; 6852</t>
+          <t>741; 6975</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 7475</t>
+          <t>0; 7081</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5691; 15282</t>
+          <t>5547; 15012</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5425; 15276</t>
+          <t>5446; 15274</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>746; 6893</t>
+          <t>1003; 7839</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1334; 9712</t>
+          <t>1042; 10170</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$medico-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$medico-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -799,12 +799,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -867,34 +867,34 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 55,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 74,22</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 49,83</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 66,23</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -907,12 +907,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,73</t>
+          <t>0,0; 44,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,76</t>
+          <t>0,0; 64,6</t>
         </is>
       </c>
     </row>
@@ -929,32 +929,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>29,2%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>15,34%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>29,2%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,54</t>
+          <t>7,53; 59,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 48,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 58,31</t>
+          <t>0,0; 63,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,61; 50,63</t>
+          <t>9,7; 46,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,49</t>
+          <t>0,0; 27,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16,22%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17,49%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18,66%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>16,01%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 38,15</t>
+          <t>5,06; 40,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,48; 33,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,13; 43,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 41,41</t>
+          <t>4,69; 36,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,08; 35,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 44,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 34,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,59; 32,51</t>
+          <t>7,27; 31,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 22,76</t>
+          <t>4,26; 21,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 26,89</t>
+          <t>3,23; 30,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,24</t>
+          <t>0,0; 14,78</t>
         </is>
       </c>
     </row>
@@ -1209,34 +1209,34 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,82%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,99%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>53,7%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>28,22%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>16,87%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>11,82%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>21,91%</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 36,41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 31,29</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4,72; 39,01</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,84</t>
+          <t>0,0; 78,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,47</t>
+          <t>4,78; 42,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,69; 40,02</t>
+          <t>4,5; 35,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,93; 28,41</t>
+          <t>5,04; 27,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,77</t>
+          <t>0,0; 70,89</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 38,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,45</t>
+          <t>0,0; 32,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,3%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11,16%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>10,04%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>4,49%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,72%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,3%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,81; 21,11</t>
+          <t>7,25; 24,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,88</t>
+          <t>5,73; 17,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,81; 17,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,43</t>
+          <t>0,0; 33,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,75; 23,95</t>
+          <t>3,81; 22,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,25; 17,28</t>
+          <t>1,23; 12,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 17,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,46</t>
+          <t>0,0; 27,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,0; 18,94</t>
+          <t>6,31; 19,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 12,6</t>
+          <t>4,55; 12,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 12,47</t>
+          <t>1,18; 11,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 24,69</t>
+          <t>3,1; 25,23</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t>739</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1516</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>2509</t>
         </is>
       </c>
     </row>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3261</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2533</t>
+          <t>0; 4986</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2942</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4777</t>
+          <t>0; 2569</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3723</t>
+          <t>0; 3515</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 6019</t>
+          <t>0; 5999</t>
         </is>
       </c>
     </row>
@@ -2207,14 +2207,14 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2227,12 +2227,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2275,32 +2275,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2516</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>580</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2516</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2476</t>
+          <t>648; 5094</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2926</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>645; 5024</t>
+          <t>0; 2401</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3411</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1191; 6275</t>
+          <t>1202; 5801</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 3383</t>
+          <t>0; 3330</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2420,37 +2420,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,62 +2483,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4241</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2036</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2357</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>4241</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>2301</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>4394</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>4241</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>308</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>592; 4851</t>
+          <t>736; 5920</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1571; 8034</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>633; 5390</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2109</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>736; 6018</t>
+          <t>597; 4678</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1717; 8520</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>647; 5468</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1806</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2067; 8857</t>
+          <t>1980; 8705</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1791; 9129</t>
+          <t>1707; 8618</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>642; 5478</t>
+          <t>658; 6239</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 2275</t>
+          <t>0; 1713</t>
         </is>
       </c>
     </row>
@@ -2623,34 +2623,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>806</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2236</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1322</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1353</t>
-        </is>
-      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>957</t>
         </is>
       </c>
     </row>
@@ -2759,12 +2759,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2856</t>
+          <t>0; 4074</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>625; 5173</t>
+          <t>0; 4236</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2774,17 +2774,17 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1783</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4346</t>
+          <t>0; 2240</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4260</t>
+          <t>634; 5636</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2794,17 +2794,17 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 1826</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>659; 5622</t>
+          <t>632; 5022</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1320; 7614</t>
+          <t>1350; 7315</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3052</t>
+          <t>0; 3097</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3512</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3542</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 3433</t>
+          <t>0; 3644</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3039,37 +3039,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3107,62 +3107,62 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>6195</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>7358</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2483</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>3422</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2236</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1402</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>6195</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>7358</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>9617</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>9595</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
           <t>3040</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>9617</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>9595</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
-      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3774</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1300; 7195</t>
+          <t>3272; 11076</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>609; 5913</t>
+          <t>4097; 12778</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>739; 7259</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 5219</t>
+          <t>0; 7549</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3047; 10815</t>
+          <t>1300; 7519</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3750; 12343</t>
+          <t>613; 6253</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>741; 6975</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 7081</t>
+          <t>0; 4756</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5547; 15012</t>
+          <t>4997; 15124</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5446; 15274</t>
+          <t>5513; 15155</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1003; 7839</t>
+          <t>741; 7070</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1042; 10170</t>
+          <t>1223; 9950</t>
         </is>
       </c>
     </row>
